--- a/data/attendance/AMPHI_عراس_فلسفة_ادبي.xlsx
+++ b/data/attendance/AMPHI_عراس_فلسفة_ادبي.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D4ECD5-B033-4DF5-AE31-67DE9A0DAD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B526B74C-2269-486C-99A1-37102891B0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,9 +516,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
-  <si>
-    <t>عراس فلسفة ادبي  |  AMPHI  |  BAC  |  لمياء عراس</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+  <si>
+    <t>عراس فلسفة ادبي  |  AMPHI  |  BAC  |  عراس لمياء</t>
   </si>
   <si>
     <t>class_id=12</t>
@@ -537,12 +537,6 @@
   </si>
   <si>
     <t>الاسم واللقب</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
   </si>
   <si>
     <t/>
@@ -808,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -837,6 +831,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1263,41 +1260,41 @@
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="11">
+        <v>46276</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46283</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1305,13 +1302,13 @@
         <v>170</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
@@ -1349,13 +1346,13 @@
         <v>270</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="7">
         <v>0</v>
       </c>
       <c r="D6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -1393,7 +1390,7 @@
         <v>405</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6">
         <v>0</v>
@@ -1437,13 +1434,13 @@
         <v>447</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7">
         <v>0</v>
@@ -1481,13 +1478,13 @@
         <v>453</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
         <v>0</v>
@@ -1525,13 +1522,13 @@
         <v>455</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7">
         <v>0</v>
@@ -1569,13 +1566,13 @@
         <v>458</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" s="6">
         <v>0</v>
       </c>
       <c r="D11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="6">
         <v>0</v>
@@ -1613,13 +1610,13 @@
         <v>460</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7">
         <v>0</v>
@@ -1657,13 +1654,13 @@
         <v>463</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6">
         <v>0</v>
@@ -1701,13 +1698,13 @@
         <v>465</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C14" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7">
         <v>0</v>
@@ -1745,13 +1742,13 @@
         <v>469</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6">
         <v>0</v>
@@ -1789,13 +1786,13 @@
         <v>477</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="7">
         <v>0</v>
       </c>
       <c r="D16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7">
         <v>0</v>
@@ -1833,13 +1830,13 @@
         <v>479</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
@@ -1877,13 +1874,13 @@
         <v>480</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7">
         <v>0</v>
@@ -1921,13 +1918,13 @@
         <v>481</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6">
         <v>0</v>
@@ -1965,13 +1962,13 @@
         <v>482</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C20" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7">
         <v>0</v>
@@ -2009,10 +2006,10 @@
         <v>483</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -2053,7 +2050,7 @@
         <v>484</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7">
         <v>0</v>
@@ -2097,7 +2094,7 @@
         <v>485</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -2141,7 +2138,7 @@
         <v>486</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" s="7">
         <v>0</v>
@@ -2185,7 +2182,7 @@
         <v>487</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" s="6">
         <v>1</v>
@@ -2229,7 +2226,7 @@
         <v>488</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C26" s="7">
         <v>0</v>
@@ -2273,7 +2270,7 @@
         <v>489</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" s="6">
         <v>0</v>
@@ -2317,7 +2314,7 @@
         <v>490</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7">
         <v>0</v>
@@ -2361,7 +2358,7 @@
         <v>491</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C29" s="6">
         <v>0</v>
@@ -2405,7 +2402,7 @@
         <v>492</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C30" s="7">
         <v>0</v>
@@ -2449,7 +2446,7 @@
         <v>493</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
@@ -2493,7 +2490,7 @@
         <v>494</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C32" s="7">
         <v>0</v>
@@ -2537,7 +2534,7 @@
         <v>495</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C33" s="6">
         <v>0</v>
@@ -2581,7 +2578,7 @@
         <v>496</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C34" s="7">
         <v>0</v>
@@ -2625,7 +2622,7 @@
         <v>497</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C35" s="6">
         <v>0</v>
@@ -2669,7 +2666,7 @@
         <v>584</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="7">
         <v>0</v>
@@ -2713,7 +2710,7 @@
         <v>585</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37" s="6">
         <v>0</v>
@@ -2757,7 +2754,7 @@
         <v>586</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C38" s="7">
         <v>0</v>
@@ -2801,7 +2798,7 @@
         <v>587</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C39" s="6">
         <v>0</v>
@@ -2864,77 +2861,77 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
